--- a/docs/enterprise-context/synthetic/apexretail/06-renewal-calendar.xlsx
+++ b/docs/enterprise-context/synthetic/apexretail/06-renewal-calendar.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="212">
   <si>
     <t>Dataset</t>
   </si>
@@ -450,6 +450,87 @@
     <t>REN-VEN-GENESYS</t>
   </si>
   <si>
+    <t>REN-RELEX-2027</t>
+  </si>
+  <si>
+    <t>CON-RELEX-2026</t>
+  </si>
+  <si>
+    <t>VEN-RELEX</t>
+  </si>
+  <si>
+    <t>2027-10-28</t>
+  </si>
+  <si>
+    <t>2026-04-15</t>
+  </si>
+  <si>
+    <t>Finance Technology</t>
+  </si>
+  <si>
+    <t>REN-VEN-RELEX</t>
+  </si>
+  <si>
+    <t>REN-SNOW-2027</t>
+  </si>
+  <si>
+    <t>CON-SNOW-2026</t>
+  </si>
+  <si>
+    <t>VEN-SNOW</t>
+  </si>
+  <si>
+    <t>2027-11-28</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>REN-VEN-SNOW</t>
+  </si>
+  <si>
+    <t>REN-MICROSOFT-2027</t>
+  </si>
+  <si>
+    <t>CON-MICROSOFT-2026</t>
+  </si>
+  <si>
+    <t>VEN-MICROSOFT</t>
+  </si>
+  <si>
+    <t>2027-12-28</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>REN-VEN-MICROSOFT</t>
+  </si>
+  <si>
+    <t>REN-AWS-2027</t>
+  </si>
+  <si>
+    <t>CON-AWS-2026</t>
+  </si>
+  <si>
+    <t>VEN-AWS</t>
+  </si>
+  <si>
+    <t>REN-VEN-AWS</t>
+  </si>
+  <si>
+    <t>REN-AZURE-2027</t>
+  </si>
+  <si>
+    <t>CON-AZURE-2026</t>
+  </si>
+  <si>
+    <t>VEN-AZURE</t>
+  </si>
+  <si>
+    <t>REN-VEN-AZURE</t>
+  </si>
+  <si>
     <t>REN-DATABRICKS-2027</t>
   </si>
   <si>
@@ -459,76 +540,7 @@
     <t>VEN-DATABRICKS</t>
   </si>
   <si>
-    <t>2027-10-28</t>
-  </si>
-  <si>
-    <t>2026-04-15</t>
-  </si>
-  <si>
-    <t>Finance Technology</t>
-  </si>
-  <si>
     <t>REN-VEN-DATABRICKS</t>
-  </si>
-  <si>
-    <t>REN-SNOW-2027</t>
-  </si>
-  <si>
-    <t>CON-SNOW-2026</t>
-  </si>
-  <si>
-    <t>VEN-SNOW</t>
-  </si>
-  <si>
-    <t>2027-11-28</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>REN-VEN-SNOW</t>
-  </si>
-  <si>
-    <t>REN-MICROSOFT-2027</t>
-  </si>
-  <si>
-    <t>CON-MICROSOFT-2026</t>
-  </si>
-  <si>
-    <t>VEN-MICROSOFT</t>
-  </si>
-  <si>
-    <t>2027-12-28</t>
-  </si>
-  <si>
-    <t>2026-06-15</t>
-  </si>
-  <si>
-    <t>REN-VEN-MICROSOFT</t>
-  </si>
-  <si>
-    <t>REN-AWS-2027</t>
-  </si>
-  <si>
-    <t>CON-AWS-2026</t>
-  </si>
-  <si>
-    <t>VEN-AWS</t>
-  </si>
-  <si>
-    <t>REN-VEN-AWS</t>
-  </si>
-  <si>
-    <t>REN-AZURE-2027</t>
-  </si>
-  <si>
-    <t>CON-AZURE-2026</t>
-  </si>
-  <si>
-    <t>VEN-AZURE</t>
-  </si>
-  <si>
-    <t>REN-VEN-AZURE</t>
   </si>
   <si>
     <t>REN-SNOWFLAKE-2027</t>
@@ -2277,13 +2289,13 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="C16" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="D16" t="s">
         <v>99</v>
@@ -2313,7 +2325,7 @@
         <v>82</v>
       </c>
       <c r="M16" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="N16" t="s">
         <v>84</v>
@@ -2333,13 +2345,13 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B17" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C17" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D17" t="s">
         <v>106</v>
@@ -2369,7 +2381,7 @@
         <v>82</v>
       </c>
       <c r="M17" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="N17" t="s">
         <v>84</v>
@@ -2389,13 +2401,13 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B18" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C18" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D18" t="s">
         <v>114</v>
@@ -2425,7 +2437,7 @@
         <v>82</v>
       </c>
       <c r="M18" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="N18" t="s">
         <v>84</v>
@@ -2445,13 +2457,13 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B19" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C19" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D19" t="s">
         <v>121</v>
@@ -2481,7 +2493,7 @@
         <v>82</v>
       </c>
       <c r="M19" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="N19" t="s">
         <v>84</v>
@@ -2501,13 +2513,13 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B20" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C20" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D20" t="s">
         <v>128</v>
@@ -2537,7 +2549,7 @@
         <v>82</v>
       </c>
       <c r="M20" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="N20" t="s">
         <v>84</v>
@@ -2557,13 +2569,13 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B21" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C21" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D21" t="s">
         <v>135</v>
@@ -2593,7 +2605,7 @@
         <v>82</v>
       </c>
       <c r="M21" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="N21" t="s">
         <v>84</v>
@@ -2613,13 +2625,13 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B22" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C22" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D22" t="s">
         <v>142</v>
@@ -2649,7 +2661,7 @@
         <v>82</v>
       </c>
       <c r="M22" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="N22" t="s">
         <v>84</v>
@@ -2669,13 +2681,13 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B23" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C23" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D23" t="s">
         <v>148</v>
@@ -2705,7 +2717,7 @@
         <v>82</v>
       </c>
       <c r="M23" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N23" t="s">
         <v>84</v>
@@ -2725,13 +2737,13 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C24" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D24" t="s">
         <v>155</v>
@@ -2761,7 +2773,7 @@
         <v>82</v>
       </c>
       <c r="M24" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="N24" t="s">
         <v>84</v>
@@ -2781,13 +2793,13 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B25" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C25" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D25" t="s">
         <v>161</v>
@@ -2817,7 +2829,7 @@
         <v>82</v>
       </c>
       <c r="M25" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="N25" t="s">
         <v>84</v>
